--- a/data/05_modelado/results/results_lineales_basico.xlsx
+++ b/data/05_modelado/results/results_lineales_basico.xlsx
@@ -542,52 +542,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7564983454614655</v>
+        <v>0.8131796087496491</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006123515596986275</v>
+        <v>0.00419568457480829</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9055556282596344</v>
+        <v>0.9406270456816881</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003415658412659005</v>
+        <v>0.002782745062362623</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7119822164425902</v>
+        <v>0.7714923513771932</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8071431744875202</v>
+        <v>0.8597763562531957</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8480070299547116</v>
+        <v>0.8844438063210157</v>
       </c>
       <c r="K2" t="n">
-        <v>112.901</v>
+        <v>98.999</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>6.66</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7623</v>
+        <v>0.8208</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9142</v>
+        <v>0.9467</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7079</v>
+        <v>0.7706</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8256</v>
+        <v>0.878</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8494</v>
+        <v>0.8879</v>
       </c>
       <c r="R2" t="n">
-        <v>0.653</v>
+        <v>0.7397</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3252</v>
+        <v>0.2582</v>
       </c>
     </row>
     <row r="3">
@@ -607,52 +607,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7582709660512823</v>
+        <v>0.8154857186662795</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004171604488190237</v>
+        <v>0.005645496372671115</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9032101966333258</v>
+        <v>0.939318345902185</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00242878605028493</v>
+        <v>0.002834520714023874</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7225322042312822</v>
+        <v>0.7875058981612502</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7979907928504441</v>
+        <v>0.8456650545942448</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8511674686979726</v>
+        <v>0.8880503140742153</v>
       </c>
       <c r="K3" t="n">
-        <v>448.563</v>
+        <v>170.355</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7613</v>
+        <v>0.8183</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9126</v>
+        <v>0.9458</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7163</v>
+        <v>0.7816</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8124</v>
+        <v>0.8587</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.851</v>
+        <v>0.8885</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6536</v>
+        <v>0.7381</v>
       </c>
       <c r="S3" t="n">
-        <v>0.357</v>
+        <v>0.2797</v>
       </c>
     </row>
     <row r="4">
@@ -672,52 +672,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7400158105610716</v>
+        <v>0.8098878515300243</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001999545657618309</v>
+        <v>0.001438437931955519</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9000351655149885</v>
+        <v>0.9359077674488931</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00386559300205514</v>
+        <v>0.002933434465342158</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8241293282827232</v>
+        <v>0.871526206690789</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6716241595992087</v>
+        <v>0.7565469877240699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8619868675580584</v>
+        <v>0.8961183481679752</v>
       </c>
       <c r="K4" t="n">
-        <v>109.93</v>
+        <v>80.964</v>
       </c>
       <c r="L4" t="n">
-        <v>5.01</v>
+        <v>6.78</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7541</v>
+        <v>0.8158</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9083</v>
+        <v>0.9428</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8293</v>
+        <v>0.8703</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6914</v>
+        <v>0.7677</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8681</v>
+        <v>0.8986</v>
       </c>
       <c r="R4" t="n">
-        <v>0.665</v>
+        <v>0.7462</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3283</v>
+        <v>0.2597</v>
       </c>
     </row>
     <row r="5">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7215904896594297</v>
+        <v>0.7550972149437635</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00357759049344102</v>
+        <v>0.006871686473038936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8850984813019854</v>
+        <v>0.9109499135777416</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004869039549467532</v>
+        <v>0.004286400054514685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6528527229086913</v>
+        <v>0.6875271951410917</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8067637572084841</v>
+        <v>0.8376554483981998</v>
       </c>
       <c r="J5" t="n">
-        <v>0.81796543213972</v>
+        <v>0.8410914744175857</v>
       </c>
       <c r="K5" t="n">
-        <v>6.807</v>
+        <v>1.926</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7288</v>
+        <v>0.7601</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8912</v>
+        <v>0.9161</v>
       </c>
       <c r="O5" t="n">
-        <v>0.653</v>
+        <v>0.6881</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8246</v>
+        <v>0.849</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8205</v>
+        <v>0.8433</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5974</v>
+        <v>0.6456</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4183</v>
+        <v>0.3731</v>
       </c>
     </row>
     <row r="6">
@@ -802,52 +802,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7236380792058493</v>
+        <v>0.7554974623059211</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003262651308187069</v>
+        <v>0.007898496562435691</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8850131604431113</v>
+        <v>0.9105889776283842</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004830727805954928</v>
+        <v>0.004398031409553485</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6592766700839555</v>
+        <v>0.691385867513496</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8021871624967385</v>
+        <v>0.8329515465474806</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8208282657809421</v>
+        <v>0.8423183991717756</v>
       </c>
       <c r="K6" t="n">
-        <v>6.385</v>
+        <v>3.339</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M6" t="n">
-        <v>0.731</v>
+        <v>0.7614</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8911</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6581</v>
+        <v>0.6926</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.8454</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.823</v>
+        <v>0.8451</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6016</v>
+        <v>0.6484</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4137</v>
+        <v>0.3696</v>
       </c>
     </row>
     <row r="7">
@@ -867,63 +867,63 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7200656311241855</v>
+        <v>0.7490915130761712</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009654675623845083</v>
+        <v>0.004167737120005451</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8845935644281168</v>
+        <v>0.9103383330709626</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004943200072061573</v>
+        <v>0.004736296862742382</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7756228114556811</v>
+        <v>0.7927372623217182</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6721329842618973</v>
+        <v>0.7105256185422525</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8472262225880488</v>
+        <v>0.8608342093132387</v>
       </c>
       <c r="K7" t="n">
-        <v>5.926</v>
+        <v>3.013</v>
       </c>
       <c r="L7" t="n">
-        <v>5.32</v>
+        <v>6.92</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7222</v>
+        <v>0.7577</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8911</v>
+        <v>0.9153</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7658</v>
+        <v>0.7899</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6833</v>
+        <v>0.728</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8462</v>
+        <v>0.8638</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.6632</v>
       </c>
       <c r="S7" t="n">
-        <v>0.365</v>
+        <v>0.3263</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SVM_lineal</t>
+          <t>LDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,58 +932,58 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7255033237336189</v>
+        <v>0.7529516133446159</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006104318062521838</v>
+        <v>0.005847307384366608</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8843576981597293</v>
+        <v>0.90952151997194</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004359519374954015</v>
+        <v>0.003815404540050895</v>
       </c>
       <c r="H8" t="n">
-        <v>0.664561018718131</v>
+        <v>0.6856266400359575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7990083613971797</v>
+        <v>0.8351127791003036</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8232077312915227</v>
+        <v>0.8397158991562257</v>
       </c>
       <c r="K8" t="n">
-        <v>222.988</v>
+        <v>0.87</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7307</v>
+        <v>0.7565</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8894</v>
+        <v>0.9146</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6602</v>
+        <v>0.6832</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8475</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8236</v>
+        <v>0.8404</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6018</v>
+        <v>0.6399</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3695</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LDA</t>
+          <t>SVM_lineal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -997,52 +997,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7249502786152631</v>
+        <v>0.7566461040751585</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00626459617405727</v>
+        <v>0.006902453984135339</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8843329932241243</v>
+        <v>0.9081345416562769</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004412754167309445</v>
+        <v>0.004032424685030564</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6599831817691921</v>
+        <v>0.696688403837072</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8043477488204299</v>
+        <v>0.8281202567791455</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8215346269500488</v>
+        <v>0.8442146209512279</v>
       </c>
       <c r="K9" t="n">
-        <v>3.107</v>
+        <v>146.073</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M9" t="n">
-        <v>0.728</v>
+        <v>0.7634</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8898</v>
+        <v>0.9144</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6538</v>
+        <v>0.6969</v>
       </c>
       <c r="P9" t="n">
-        <v>0.821</v>
+        <v>0.8439</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8205</v>
+        <v>0.847</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5966</v>
+        <v>0.6518</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4215</v>
+        <v>0.3747</v>
       </c>
     </row>
     <row r="10">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1062,58 +1062,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7266021910022269</v>
+        <v>0.7552133614589875</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005461443680121344</v>
+        <v>0.007235999710313818</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8839391384077853</v>
+        <v>0.9078242602398875</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00432949259336935</v>
+        <v>0.003887058137010558</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6664119892739955</v>
+        <v>0.6925465999302066</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7990086845117457</v>
+        <v>0.8305362651671997</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8241744813749741</v>
+        <v>0.842541523520838</v>
       </c>
       <c r="K10" t="n">
-        <v>313.818</v>
+        <v>75.029</v>
       </c>
       <c r="L10" t="n">
-        <v>5.01</v>
+        <v>6.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7322</v>
+        <v>0.7624</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8892</v>
+        <v>0.914</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6627</v>
+        <v>0.6918</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.849</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.825</v>
+        <v>0.8452</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6494</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4181</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SVM_lineal</t>
+          <t>LDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1127,52 +1127,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7198124238707404</v>
+        <v>0.7454656595468206</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008186755279267368</v>
+        <v>0.003291535615744811</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8829966625011728</v>
+        <v>0.9072716669671005</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004634565943259712</v>
+        <v>0.004042803272633883</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7781570502099299</v>
+        <v>0.7862751778567668</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6698444445701002</v>
+        <v>0.7091274210368586</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8475608849228481</v>
+        <v>0.858380290694018</v>
       </c>
       <c r="K11" t="n">
-        <v>196.844</v>
+        <v>2.364</v>
       </c>
       <c r="L11" t="n">
-        <v>5.14</v>
+        <v>6.63</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7236</v>
+        <v>0.7466</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8898</v>
+        <v>0.912</v>
       </c>
       <c r="O11" t="n">
-        <v>0.773</v>
+        <v>0.7783</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6802</v>
+        <v>0.7173</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.848</v>
+        <v>0.8575</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6194</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3656</v>
+        <v>0.3371</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1192,63 +1192,63 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.714960077452233</v>
+        <v>0.7454656595468206</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01017420782088104</v>
+        <v>0.003291535615744811</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8823181498223265</v>
+        <v>0.9072716669671005</v>
       </c>
       <c r="G12" t="n">
-        <v>0.004427890999659801</v>
+        <v>0.004042803272633883</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7588041582669012</v>
+        <v>0.7862751778567668</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6762009966468786</v>
+        <v>0.7091274210368586</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8423927486141547</v>
+        <v>0.858380290694018</v>
       </c>
       <c r="K12" t="n">
-        <v>4.421</v>
+        <v>1.663</v>
       </c>
       <c r="L12" t="n">
-        <v>5.14</v>
+        <v>6.63</v>
       </c>
       <c r="M12" t="n">
-        <v>0.726</v>
+        <v>0.7466</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8887</v>
+        <v>0.912</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7599</v>
+        <v>0.7783</v>
       </c>
       <c r="P12" t="n">
-        <v>0.695</v>
+        <v>0.7173</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8465</v>
+        <v>0.8575</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6197</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>0.37</v>
+        <v>0.3371</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LDA</t>
+          <t>SVM_lineal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1257,52 +1257,52 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.714960077452233</v>
+        <v>0.7487598873695469</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01017420782088104</v>
+        <v>0.004590734269444388</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8823181498223265</v>
+        <v>0.9054210519767842</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004427890999659801</v>
+        <v>0.004775983310566349</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7588041582669012</v>
+        <v>0.8012342359450247</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6762009966468786</v>
+        <v>0.7031519018119458</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8423927486141547</v>
+        <v>0.8620239800794913</v>
       </c>
       <c r="K13" t="n">
-        <v>5.021</v>
+        <v>65.28</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>6.78</v>
       </c>
       <c r="M13" t="n">
-        <v>0.726</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8887</v>
+        <v>0.9109</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7599</v>
+        <v>0.7963</v>
       </c>
       <c r="P13" t="n">
-        <v>0.695</v>
+        <v>0.7133</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8465</v>
+        <v>0.8628</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6197</v>
+        <v>0.6579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.37</v>
+        <v>0.3317</v>
       </c>
     </row>
   </sheetData>
